--- a/media/Levels/kakeraMapDateLevels2.xlsx
+++ b/media/Levels/kakeraMapDateLevels2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yuuta\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\デスクトップ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yuuta\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\ドキュメント\2024年３月特別授業\BaseCross64\DoctorRemote\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CD7A9E8-F0E8-4E1C-B996-8DB70F57482E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5376DEFE-A858-45C1-918D-36830ABC10B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BDE0F5B9-DF54-47AF-B1A2-D8190B03E7B5}"/>
   </bookViews>
@@ -637,7 +637,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -654,9 +654,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -7623,7 +7620,7 @@
       <c r="CE15">
         <v>0</v>
       </c>
-      <c r="CF15" s="6">
+      <c r="CF15">
         <v>0</v>
       </c>
       <c r="CG15">
@@ -17136,7 +17133,7 @@
       <c r="CL36">
         <v>0</v>
       </c>
-      <c r="CM36" s="6">
+      <c r="CM36">
         <v>1</v>
       </c>
       <c r="CN36">
@@ -33076,7 +33073,7 @@
       <c r="DZ71">
         <v>0</v>
       </c>
-      <c r="EA71" s="6">
+      <c r="EA71">
         <v>0</v>
       </c>
       <c r="EB71">
@@ -55140,7 +55137,7 @@
       <c r="CX120">
         <v>0</v>
       </c>
-      <c r="CY120" s="6">
+      <c r="CY120">
         <v>0</v>
       </c>
       <c r="CZ120">
